--- a/AUSENTE.xlsx
+++ b/AUSENTE.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppServ\www\rolux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C5D859-403A-40B5-8CA0-EA6DF7F4FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11444025-EBB1-4470-8F0C-E4AD53874942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Curso</t>
   </si>
@@ -60,61 +71,38 @@
     <t>I° A</t>
   </si>
   <si>
-    <t>Yuliana Mendicute</t>
-  </si>
-  <si>
-    <t>yuliana.mendicute@a.colsanjavier.cl</t>
-  </si>
-  <si>
-    <t>Mendicute Arechavala Juan Ignacio</t>
-  </si>
-  <si>
-    <t>jimendicute@eymgestorias.cl</t>
-  </si>
-  <si>
-    <t>Johnson Undurraga
-Maria Cecilia</t>
-  </si>
-  <si>
-    <t>cjohnson@colsanjavier.cl</t>
-  </si>
-  <si>
-    <t>a</t>
+    <t>ignacio.cano@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Cano Mardones Claudio Leonel</t>
+  </si>
+  <si>
+    <t>claudiocano@sermar.cl</t>
+  </si>
+  <si>
+    <t>Nova Zenteno Cristina Lorena</t>
+  </si>
+  <si>
+    <t>cristy.nova@gmail.com</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>Ignacio Cano</t>
   </si>
   <si>
     <t>vradulovich@colsanjavier.cl</t>
   </si>
   <si>
     <t>Formación de imágenes en espejos planos, cóncavos y convexos mediante el trazado de rayos notables, la medición de distancias y el uso de la ecuación de Gauss para analizar las características de la imagen.</t>
-  </si>
-  <si>
-    <t>Juan Felipe Vergara Morales</t>
-  </si>
-  <si>
-    <t>juan.vergara@a.colsanjavier.cl</t>
-  </si>
-  <si>
-    <t>Vergara Bosman Felipe Edurado</t>
-  </si>
-  <si>
-    <t>vergarafelipe@gmail.com</t>
-  </si>
-  <si>
-    <t>Morales Vera
-Katty Daniela</t>
-  </si>
-  <si>
-    <t>kattymorales@gmail.com</t>
-  </si>
-  <si>
-    <t>o</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,24 +117,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,8 +140,14 @@
         <fgColor rgb="FF9CC2E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -182,11 +170,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -197,17 +207,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,8 +568,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -591,67 +607,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="8" t="s">
         <v>19</v>
       </c>
     </row>

--- a/AUSENTE.xlsx
+++ b/AUSENTE.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppServ\www\rolux\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11444025-EBB1-4470-8F0C-E4AD53874942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3869F7C0-C57B-4713-9827-7927E1DBCCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="1485" windowWidth="18165" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="99">
   <si>
     <t>Curso</t>
   </si>
@@ -62,47 +54,286 @@
     <t>S</t>
   </si>
   <si>
-    <t>PJ</t>
-  </si>
-  <si>
     <t>Contenido</t>
   </si>
   <si>
+    <t>I° B</t>
+  </si>
+  <si>
+    <t>Merino Rawlins Emilia Francisca</t>
+  </si>
+  <si>
+    <t>emilia.merino@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Merino Daza Juan Francisco</t>
+  </si>
+  <si>
+    <t>juanfranciscomerinodaza@gmail.com</t>
+  </si>
+  <si>
+    <t>Rawlins Robles Alejandra Carolina</t>
+  </si>
+  <si>
+    <t>alerawlins@hotmail.com</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>Enviar</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>hora</t>
+  </si>
+  <si>
     <t>I° A</t>
   </si>
   <si>
-    <t>ignacio.cano@a.colsanjavier.cl</t>
-  </si>
-  <si>
-    <t>Cano Mardones Claudio Leonel</t>
-  </si>
-  <si>
-    <t>claudiocano@sermar.cl</t>
-  </si>
-  <si>
-    <t>Nova Zenteno Cristina Lorena</t>
-  </si>
-  <si>
-    <t>cristy.nova@gmail.com</t>
+    <t>Fleckenstein Wunderlich Verena Marianne</t>
+  </si>
+  <si>
+    <t>verena.fleckenstein@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Fleckenstein Figueroa Rolf Eugenio</t>
+  </si>
+  <si>
+    <t>rflecken@yahoo.com</t>
+  </si>
+  <si>
+    <t>Wunderlich Kahler Heidi Marlene</t>
+  </si>
+  <si>
+    <t>heidiw2003@yahoo.com</t>
+  </si>
+  <si>
+    <t>Mansilla Suárez Bruno Amaru</t>
+  </si>
+  <si>
+    <t>bruno.mansilla@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Mansilla Loncomilla Cristián Mauricio</t>
+  </si>
+  <si>
+    <t>cmansillaloncomilla@gmail.com</t>
+  </si>
+  <si>
+    <t>Suárez Rioseco Nilda Loreto</t>
+  </si>
+  <si>
+    <t>loretosuarezr@gmail.com</t>
   </si>
   <si>
     <t>o</t>
   </si>
   <si>
-    <t>Ignacio Cano</t>
-  </si>
-  <si>
-    <t>vradulovich@colsanjavier.cl</t>
-  </si>
-  <si>
-    <t>Formación de imágenes en espejos planos, cóncavos y convexos mediante el trazado de rayos notables, la medición de distancias y el uso de la ecuación de Gauss para analizar las características de la imagen.</t>
+    <t>Mattos Mattos Kiara Rayén</t>
+  </si>
+  <si>
+    <t>kiara.mattos@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Mattos Mansilla Ailen Micaela</t>
+  </si>
+  <si>
+    <t>miriammansillav@gmail.com</t>
+  </si>
+  <si>
+    <t>Óptica geométrica de espejos y lentes, la visión.
+Formación de imágenes en espejos planos, cóncavos y convexos mediante el trazado de rayos notables, la medición de distancias y el uso de la ecuación de Gauss para analizar las características de la imagen. 
+La visión, defectos y correcciones.</t>
+  </si>
+  <si>
+    <t>Román Sepúlveda Emilia Ignacia</t>
+  </si>
+  <si>
+    <t>emilia.roman@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Roman Gonzalez Luis Felipe</t>
+  </si>
+  <si>
+    <t>luisfeliperoman@gmail.com</t>
+  </si>
+  <si>
+    <t>Sepulveda Undurraga Patricia Paola</t>
+  </si>
+  <si>
+    <t>ppsepulvedau@gmail.com</t>
+  </si>
+  <si>
+    <t>enviado</t>
+  </si>
+  <si>
+    <t>II° C</t>
+  </si>
+  <si>
+    <t>CHELECH SALDIVIA NASSIRA JADE</t>
+  </si>
+  <si>
+    <t>KOCHIFAS SANDOVAL MAXIMILIANO ALONSO</t>
+  </si>
+  <si>
+    <t>PAREDES ÁVILA AGUSTÍN ALBERTO</t>
+  </si>
+  <si>
+    <t>WOLLETER VELÁSQUEZ EDUARDO NICOLÁS</t>
+  </si>
+  <si>
+    <t>II° A</t>
+  </si>
+  <si>
+    <t>DÍAZ LANTAÑO CRISTÓBAL ANDRÉS</t>
+  </si>
+  <si>
+    <t>ESPINOZA RECABARREN ALONSO CRISTÓBAL</t>
+  </si>
+  <si>
+    <t>GONZÁLEZ CARVAJAL ALONSO DAVID</t>
+  </si>
+  <si>
+    <t>JIMÉNEZ SANHUEZA LAURA ISABEL DEL CARMEN</t>
+  </si>
+  <si>
+    <t>nassira.chelech@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Chelech Olavarría Hassen</t>
+  </si>
+  <si>
+    <t>hassenchelecholavarria2@gmail.com</t>
+  </si>
+  <si>
+    <t>Saldivia Saldivia Susana Haydee</t>
+  </si>
+  <si>
+    <t>susan.saldivia.1988@gmail.com</t>
+  </si>
+  <si>
+    <t>maximiliano.kochifas@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Kochifas Aros Milton Alejandro</t>
+  </si>
+  <si>
+    <t>miltonkochifas@gmail.com</t>
+  </si>
+  <si>
+    <t>Sandoval Saldivia Cynthia Karola</t>
+  </si>
+  <si>
+    <t>cynthiasandovalsa@gmail.com</t>
+  </si>
+  <si>
+    <t>agustin.paredes@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Paredes Triviño Cesar Ramon</t>
+  </si>
+  <si>
+    <t>cesar.paredes@escuelamiramar.cl</t>
+  </si>
+  <si>
+    <t>Avila Almonacid Paulina Andrea</t>
+  </si>
+  <si>
+    <t>paulina.avila.almonacid@gmail.com</t>
+  </si>
+  <si>
+    <t>eduardo.wolleter@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Wolleter Barria Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>sewolleter@gmail.com</t>
+  </si>
+  <si>
+    <t>Velasquez Gallegos Telma Mayola</t>
+  </si>
+  <si>
+    <t>MAVEGA73@YAHOO.COM</t>
+  </si>
+  <si>
+    <t>cristobal.diaz@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Diaz Cárdenas Christian Alexis</t>
+  </si>
+  <si>
+    <t>chdcdr@gmail.com</t>
+  </si>
+  <si>
+    <t>Lantaño Pinto Carolina Angelica</t>
+  </si>
+  <si>
+    <t>caro.lantano@gmail.com</t>
+  </si>
+  <si>
+    <t>alonso.espinoza@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Espinoza Silva Rodrigo Andres</t>
+  </si>
+  <si>
+    <t>rodrigo.espinoza71@gmail.com</t>
+  </si>
+  <si>
+    <t>Recabarren Santibañez Ana Carola</t>
+  </si>
+  <si>
+    <t>carolapipe72@gmail.com</t>
+  </si>
+  <si>
+    <t>alonso.gonzalez@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Gonzalez Lopez David Alejandro</t>
+  </si>
+  <si>
+    <t>david.gonzalez.lopez@iff.com</t>
+  </si>
+  <si>
+    <t>Carvajal Vera Alejandra Patricia</t>
+  </si>
+  <si>
+    <t>alejandra.carvajalv@hotmail.com</t>
+  </si>
+  <si>
+    <t>laura.jimenez@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Jimenez Vergara Jose Luis</t>
+  </si>
+  <si>
+    <t>Jimenezvergara@gmail.com</t>
+  </si>
+  <si>
+    <t>Sanhueza Araneda Patricia Andrea</t>
+  </si>
+  <si>
+    <t>patricia.sanhueza@colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Evaluar la comprensión del Movimiento Rectilíneo Uniformemente Variado (MRUV) mediante el análisis conceptual, la resolución de problemas cuantitativos y la interpretación de gráficos velocidad-tiempo ( vs ).</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Tomada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +348,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,10 +369,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,6 +393,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF9CC2E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,24 +418,11 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -185,9 +433,24 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -196,12 +459,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -210,15 +476,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -305,6 +597,1147 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6852B4AE-FD76-B625-6F35-81A0E3D389CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5631C678-68B1-BF08-C2F3-D0CC48D3552C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EE9A5E0-C658-457C-A7BE-A673B344F345}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3EA0CB9-AB0A-4465-B435-D47610A7D81E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A02F6FF-07A7-46A8-AC76-FBA34EDC96CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA068D1A-D470-47C8-AD38-0EAA40D10939}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{497D35FA-865D-4EBC-A8E3-DD71710A6D14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8919A609-C660-4585-AD1F-90144DF50312}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85B76236-E62C-4CB4-B701-544E4C5A89EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08B06503-B344-459F-BC39-6F7430737655}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CD6D37D-C7F9-4CEA-8990-9BABD32245EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A93EC5DD-6A90-437C-8EEE-441EA41A6DF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26F7532A-F595-4F97-8086-6514A1E2288B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2387FE45-ADBF-40A8-B7D9-AA04542313F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D002A781-A2F7-444C-BB87-9B2585BC1995}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="85725" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Imagen 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B617C84-C682-4F90-882B-E64B1C574DF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11191875" y="1152525"/>
+          <a:ext cx="66675" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -316,44 +1749,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -383,12 +1816,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -427,219 +1860,800 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" customWidth="1"/>
+    <col min="4" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" style="13" customWidth="1"/>
+    <col min="14" max="26" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="8">
+        <v>46291</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="13">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="7" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>19</v>
+      <c r="J3" s="11">
+        <v>46288</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="11">
+        <v>46288</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="11">
+        <v>46288</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="11">
+        <v>46288</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K9" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K10" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K11" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K12" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K13" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="11">
+        <v>46291</v>
+      </c>
+      <c r="K14" s="19">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="M2:M100">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="3Symbols2" showValue="0">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/AUSENTE.xlsx
+++ b/AUSENTE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AppServ\www\rolux\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/MisApps/Documentos/www/rolux/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C5D859-403A-40B5-8CA0-EA6DF7F4FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC4DCA4-FEA4-464B-B076-5FBAAE56F6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="15375" windowHeight="8325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="25340" windowHeight="13240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -126,24 +126,29 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -214,74 +219,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -557,9 +494,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -623,7 +569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>

--- a/AUSENTE.xlsx
+++ b/AUSENTE.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E7ABF9-15F9-914B-9756-19C111F4E4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F9495B-2638-4D21-86EF-C3DE70F25CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t>Enviar</t>
   </si>
@@ -69,9 +82,6 @@
   </si>
   <si>
     <t>a</t>
-  </si>
-  <si>
-    <t>Fri Sep 25 2026 21:00:00 GMT-0300 (hora de verano de Chile)</t>
   </si>
   <si>
     <t>Sat Dec 30 1899 03:47:15 GMT-0442 (hora de verano de Chile)</t>
@@ -97,9 +107,6 @@
     <t>heidiw2003@yahoo.com</t>
   </si>
   <si>
-    <t>Tue Sep 22 2026 21:00:00 GMT-0300 (hora de verano de Chile)</t>
-  </si>
-  <si>
     <t>Sat Dec 30 1899 10:47:15 GMT-0442 (hora de verano de Chile)</t>
   </si>
   <si>
@@ -245,6 +252,126 @@
   </si>
   <si>
     <t>patricia.sanhueza@colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Llanos Aicon Martina Andrea</t>
+  </si>
+  <si>
+    <t>Martínez Rivera Joaquín Salvador</t>
+  </si>
+  <si>
+    <t>Prado Núñez Isidora Amanda</t>
+  </si>
+  <si>
+    <t>Aravena Bucarey María Paz</t>
+  </si>
+  <si>
+    <t>Peña Linay Diego Alonso</t>
+  </si>
+  <si>
+    <t>Toro-Moreno Meriño Gonzalo Andrés</t>
+  </si>
+  <si>
+    <t>gonzalo.toro-moreno@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Vásquez Sandoval Román Alonso</t>
+  </si>
+  <si>
+    <t>roman.vasquez@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>maria.aravena@a.colsanjavier.cl</t>
+    </r>
+  </si>
+  <si>
+    <t>hectoraravenar@gmail.com</t>
+  </si>
+  <si>
+    <t>sandrabucarey03@gmail.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1155CC"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>diego.pena@a.colsanjavier.cl</t>
+    </r>
+  </si>
+  <si>
+    <t>colibrispabotilleria@gmail.com</t>
+  </si>
+  <si>
+    <t>sergio_233@msn.com</t>
+  </si>
+  <si>
+    <t>mmerino270918@gmail.com</t>
+  </si>
+  <si>
+    <t>felipe.vasquez.vet@gmail.com</t>
+  </si>
+  <si>
+    <t>karin.sandoval.velasquez@gmail.com</t>
+  </si>
+  <si>
+    <t>I° C</t>
+  </si>
+  <si>
+    <t>Revillard San Martín Antonella Paz</t>
+  </si>
+  <si>
+    <t>antonella.revillard@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Sayeg Muñoz Cristóbal Felipe</t>
+  </si>
+  <si>
+    <t>cristobal.sayeg@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>Chávez Vargas Sofía Isidora</t>
+  </si>
+  <si>
+    <t>sofia.chavez@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>III° A</t>
+  </si>
+  <si>
+    <t>III° C</t>
+  </si>
+  <si>
+    <t>martina.llanos@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>joaquin.martinez@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>isidora.prado@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>prado.riveros@gmail.com</t>
+  </si>
+  <si>
+    <t>paola.adriananunez73@gmail.com</t>
+  </si>
+  <si>
+    <t>mweisserv@gmail.com</t>
+  </si>
+  <si>
+    <t>carolina.rivera.t.cr@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -252,9 +379,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,8 +411,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1155CC"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,8 +442,14 @@
         <fgColor rgb="FF9CC2E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -345,11 +496,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,23 +599,153 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1119,6 +1463,84 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="85731" cy="179999"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EFB48A4-FD4E-4F08-B618-E275148F421D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10153650" y="1152525"/>
+          <a:ext cx="85731" cy="179999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="66680" cy="179999"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49016681-043D-4E29-A157-B7B1B1BD3DBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10153650" y="1152525"/>
+          <a:ext cx="66680" cy="179999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1127,7 +1549,7 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="171717"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -1444,19 +1866,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="13" customWidth="1"/>
-    <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="42.1640625" customWidth="1"/>
-    <col min="4" max="7" width="13.5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="18" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" style="18" customWidth="1"/>
-    <col min="10" max="22" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" customWidth="1"/>
+    <col min="4" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="16" customWidth="1"/>
+    <col min="10" max="22" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,7 +1924,7 @@
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
     </row>
-    <row r="2" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -1524,14 +1946,14 @@
       <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="J2" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="K2" s="9">
         <v>-1</v>
@@ -1548,36 +1970,36 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>27</v>
+      <c r="H3" s="19">
+        <v>46287</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="9">
         <v>1</v>
@@ -1594,7 +2016,7 @@
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -1602,28 +2024,28 @@
         <v>12</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="G4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>27</v>
+      <c r="H4" s="19">
+        <v>46287</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K4" s="9">
         <v>1</v>
@@ -1640,7 +2062,7 @@
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1648,26 +2070,26 @@
         <v>12</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>27</v>
+      <c r="H5" s="19">
+        <v>46287</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" s="9">
         <v>1</v>
@@ -1684,7 +2106,7 @@
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
@@ -1692,28 +2114,28 @@
         <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="F6" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>27</v>
+      <c r="H6" s="19">
+        <v>46287</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>25</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6" s="9">
         <v>1</v>
@@ -1730,36 +2152,36 @@
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="D7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="F7" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I7" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J7" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
@@ -1776,36 +2198,36 @@
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>40</v>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="G8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J8" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
@@ -1822,36 +2244,36 @@
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>40</v>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="G9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I9" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
@@ -1868,36 +2290,36 @@
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>40</v>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>58</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I10" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J10" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K10" s="9">
         <v>0</v>
@@ -1914,36 +2336,36 @@
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>40</v>
+    <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I11" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J11" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" s="9">
         <v>0</v>
@@ -1960,36 +2382,36 @@
       <c r="U11" s="4"/>
       <c r="V11" s="4"/>
     </row>
-    <row r="12" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>40</v>
+    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I12" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J12" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K12" s="9">
         <v>0</v>
@@ -2006,36 +2428,36 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
     </row>
-    <row r="13" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
+    <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="F13" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="G13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="20" t="s">
-        <v>19</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K13" s="9">
         <v>0</v>
@@ -2052,36 +2474,36 @@
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
     </row>
-    <row r="14" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="7" t="s">
+    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="F14" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="18">
+        <v>46290</v>
+      </c>
+      <c r="I14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>46</v>
+      <c r="J14" s="25" t="s">
+        <v>44</v>
       </c>
       <c r="K14" s="9">
         <v>0</v>
@@ -2098,17 +2520,27 @@
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="4"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="30"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -2122,17 +2554,31 @@
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="4"/>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="30"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -2146,17 +2592,31 @@
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="4"/>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="30"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -2170,17 +2630,31 @@
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="4"/>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="31"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="30"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2194,17 +2668,31 @@
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="4"/>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="31"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="30"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2218,17 +2706,31 @@
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="4"/>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="31"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="30"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2242,17 +2744,31 @@
       <c r="U20" s="4"/>
       <c r="V20" s="4"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="4"/>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="31"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="30"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2266,18 +2782,40 @@
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="36">
+        <v>46295</v>
+      </c>
+      <c r="I22" s="37">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
@@ -2290,17 +2828,25 @@
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="4"/>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="30"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2314,17 +2860,25 @@
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="4"/>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2338,17 +2892,25 @@
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="4"/>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="30"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2362,7 +2924,7 @@
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -2370,8 +2932,8 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -2386,7 +2948,7 @@
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -2394,8 +2956,8 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -2410,7 +2972,7 @@
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -2418,8 +2980,8 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -2434,7 +2996,7 @@
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2442,8 +3004,8 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -2458,7 +3020,7 @@
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -2466,8 +3028,8 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -2482,7 +3044,7 @@
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -2490,8 +3052,8 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -2506,7 +3068,7 @@
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -2514,8 +3076,8 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -2530,7 +3092,7 @@
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -2538,8 +3100,8 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -2554,7 +3116,7 @@
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -2562,8 +3124,8 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -2578,7 +3140,7 @@
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -2586,8 +3148,8 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -2602,7 +3164,7 @@
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -2610,8 +3172,8 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -2626,7 +3188,7 @@
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2634,8 +3196,8 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -2650,7 +3212,7 @@
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -2658,8 +3220,8 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -2674,7 +3236,7 @@
       <c r="U38" s="4"/>
       <c r="V38" s="4"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2682,8 +3244,8 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -2698,7 +3260,7 @@
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -2706,8 +3268,8 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -2722,6 +3284,30 @@
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
     </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/AUSENTE.xlsx
+++ b/AUSENTE.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F9495B-2638-4D21-86EF-C3DE70F25CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7DC4BE-AEB0-45F1-A00A-BFAAE6F679E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="123">
   <si>
     <t>Enviar</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Contenido</t>
   </si>
   <si>
-    <t>Tomada</t>
-  </si>
-  <si>
     <t>enviado</t>
   </si>
   <si>
@@ -82,9 +79,6 @@
   </si>
   <si>
     <t>a</t>
-  </si>
-  <si>
-    <t>Sat Dec 30 1899 03:47:15 GMT-0442 (hora de verano de Chile)</t>
   </si>
   <si>
     <t>Óptica geométrica de espejos y lentes, la visión.
@@ -107,9 +101,6 @@
     <t>heidiw2003@yahoo.com</t>
   </si>
   <si>
-    <t>Sat Dec 30 1899 10:47:15 GMT-0442 (hora de verano de Chile)</t>
-  </si>
-  <si>
     <t>Mansilla Suárez Bruno Amaru</t>
   </si>
   <si>
@@ -144,9 +135,6 @@
   </si>
   <si>
     <t>ppsepulvedau@gmail.com</t>
-  </si>
-  <si>
-    <t>si</t>
   </si>
   <si>
     <t>II° C</t>
@@ -373,15 +361,72 @@
   <si>
     <t>carolina.rivera.t.cr@gmail.com</t>
   </si>
+  <si>
+    <t>leo.tinto@gmail.com</t>
+  </si>
+  <si>
+    <t>andycorre@hotmail.com</t>
+  </si>
+  <si>
+    <t>john.revillard@gmail.com</t>
+  </si>
+  <si>
+    <t>gsmrodriguez@gmail.com</t>
+  </si>
+  <si>
+    <t>cristiansayegb@gmail.com</t>
+  </si>
+  <si>
+    <t>nellymunozmoraga@gmail.com</t>
+  </si>
+  <si>
+    <t>eduardo.chavez.c@gmail.com</t>
+  </si>
+  <si>
+    <t>evelyn.vargas.olavarria@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluar la comprensión de la formación del Sistema Solar, las características de sus planetas y cuerpos menores, junto con el entendimiento de las estructuras cósmicas, la evolución del universo y las etapas del ciclo estelar. </t>
+  </si>
+  <si>
+    <t>Evaluar la comprensión y aplicación de las Leyes de Newton, incluyendo fuerza neta, peso, normal, elástica, tensión y aceleración, así como el análisis de sistemas y situaciones físicas con y sin roce.</t>
+  </si>
+  <si>
+    <t>Postergado</t>
+  </si>
+  <si>
+    <t>Retirado</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>Listo</t>
+  </si>
+  <si>
+    <t>Grecco Jiménez Lucas Lorenzo</t>
+  </si>
+  <si>
+    <t>lucas.grecco@a.colsanjavier.cl</t>
+  </si>
+  <si>
+    <t>cristiangrecco78@gmail.com</t>
+  </si>
+  <si>
+    <t>carolajimenezmaldonado@gmail.com</t>
+  </si>
+  <si>
+    <t>Formación de imágenes en espejos planos, cóncavos y convexos mediante el trazado de rayos notables, la medición de distancias y el uso de la ecuación de Gauss para analizar las características de la imagen.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,8 +474,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,12 +516,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -519,6 +615,19 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -536,42 +645,40 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -585,34 +692,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -621,11 +713,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -633,14 +721,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -652,28 +737,135 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1866,16 +2058,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" style="13" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="10" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" customWidth="1"/>
-    <col min="4" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="16" customWidth="1"/>
-    <col min="10" max="22" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="45.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="67" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" style="12" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9" style="10" customWidth="1"/>
+    <col min="12" max="22" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1900,1417 +2096,2865 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="76" t="s">
+        <v>117</v>
+      </c>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+    </row>
+    <row r="2" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-    </row>
-    <row r="2" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="14">
+        <v>46290</v>
+      </c>
+      <c r="I2" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J2" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="18">
+      <c r="K2" s="19">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="14">
+        <v>46287</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="19">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="14">
+        <v>46287</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="19">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="14">
+        <v>46287</v>
+      </c>
+      <c r="I5" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="19">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="14">
+        <v>46287</v>
+      </c>
+      <c r="I6" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="14">
         <v>46290</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I7" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="19">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="14">
+        <v>46290</v>
+      </c>
+      <c r="I8" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="19">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="14">
+        <v>46290</v>
+      </c>
+      <c r="I9" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J9" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="19">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="34">
+        <v>46290</v>
+      </c>
+      <c r="I10" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J10" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="19">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+    </row>
+    <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="35">
+        <v>46290</v>
+      </c>
+      <c r="I11" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J11" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="19">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="35">
+        <v>46290</v>
+      </c>
+      <c r="I12" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J12" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="19">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="35">
+        <v>46290</v>
+      </c>
+      <c r="I13" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J13" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="19">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="35">
+        <v>46290</v>
+      </c>
+      <c r="I14" s="37">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J14" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="19">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="9">
-        <v>-1</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="C15" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="64">
+        <v>46295</v>
+      </c>
+      <c r="I15" s="43">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="19">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I16" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J16" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="19">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="19">
-        <v>46287</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="9">
+      <c r="C17" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="64">
+        <v>46295</v>
+      </c>
+      <c r="I17" s="43">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J17" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="K17" s="19">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="64">
+        <v>46295</v>
+      </c>
+      <c r="I18" s="43">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J18" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="19">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I19" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J19" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="K19" s="19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I20" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J20" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="19">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="65">
+        <v>46295</v>
+      </c>
+      <c r="I21" s="48">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J21" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="K21" s="19">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I22" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J22" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="19">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I23" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J23" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="K23" s="19">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I24" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J24" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24" s="19">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="35">
+        <v>46295</v>
+      </c>
+      <c r="I25" s="24">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J25" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="K25" s="19">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="64">
+        <v>46302</v>
+      </c>
+      <c r="I26" s="43">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J26" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="19">
         <v>1</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="66">
+        <v>46305</v>
+      </c>
+      <c r="I27" s="60">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J27" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="19">
-        <v>46287</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="19">
-        <v>46287</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="9">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="19">
-        <v>46287</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="9">
-        <v>1</v>
-      </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I7" s="21" t="s">
+      <c r="H28" s="66">
+        <v>46305</v>
+      </c>
+      <c r="I28" s="60">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="J28" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="81">
+        <v>46309</v>
+      </c>
+      <c r="I29" s="82">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J29" s="83" t="s">
+        <v>112</v>
+      </c>
+      <c r="K29" s="84">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="C30" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="H30" s="85">
+        <v>46309</v>
+      </c>
+      <c r="I30" s="86">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="J30" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K30" s="18">
         <v>0</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-    </row>
-    <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-    </row>
-    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-    </row>
-    <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-    </row>
-    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="18">
-        <v>46290</v>
-      </c>
-      <c r="I14" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="31"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" s="31"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="31"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="31"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="36">
-        <v>46295</v>
-      </c>
-      <c r="I22" s="37">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="J22" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="12"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="85"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A32" s="12"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="12"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="85"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A36" s="12"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="12"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="85"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="85"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="88"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="89"/>
+      <c r="I42" s="90"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="88"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="88"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="88"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="88"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="88"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="88"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="89"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="88"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="88"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="89"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="88"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="88"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="88"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="88"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="88"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="88"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="88"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="88"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="88"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="88"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="89"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="88"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="88"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="88"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="88"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="28"/>
+      <c r="K53" s="88"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="88"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="88"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="88"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="88"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="88"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="89"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="88"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="88"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="88"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="88"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="88"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="88"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="89"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="88"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="88"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="88"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="88"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="90"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="88"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="88"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="89"/>
+      <c r="I62" s="90"/>
+      <c r="J62" s="28"/>
+      <c r="K62" s="88"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="88"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="89"/>
+      <c r="I63" s="90"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="88"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="88"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="89"/>
+      <c r="I64" s="90"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="88"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="88"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="28"/>
+      <c r="G65" s="28"/>
+      <c r="H65" s="89"/>
+      <c r="I65" s="90"/>
+      <c r="J65" s="28"/>
+      <c r="K65" s="88"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="88"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="28"/>
+      <c r="F66" s="28"/>
+      <c r="G66" s="28"/>
+      <c r="H66" s="89"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="28"/>
+      <c r="K66" s="88"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="88"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="89"/>
+      <c r="I67" s="90"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="88"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="88"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="90"/>
+      <c r="J68" s="28"/>
+      <c r="K68" s="88"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="88"/>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="90"/>
+      <c r="J69" s="28"/>
+      <c r="K69" s="88"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="88"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="90"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="88"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="88"/>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="89"/>
+      <c r="I71" s="90"/>
+      <c r="J71" s="28"/>
+      <c r="K71" s="88"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="88"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="89"/>
+      <c r="I72" s="90"/>
+      <c r="J72" s="28"/>
+      <c r="K72" s="88"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="88"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="89"/>
+      <c r="I73" s="90"/>
+      <c r="J73" s="28"/>
+      <c r="K73" s="88"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="88"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="89"/>
+      <c r="I74" s="90"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="88"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="88"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="89"/>
+      <c r="I75" s="90"/>
+      <c r="J75" s="28"/>
+      <c r="K75" s="88"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="88"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="89"/>
+      <c r="I76" s="90"/>
+      <c r="J76" s="28"/>
+      <c r="K76" s="88"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="88"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="89"/>
+      <c r="I77" s="90"/>
+      <c r="J77" s="28"/>
+      <c r="K77" s="88"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="88"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="89"/>
+      <c r="I78" s="90"/>
+      <c r="J78" s="28"/>
+      <c r="K78" s="88"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="88"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="89"/>
+      <c r="I79" s="90"/>
+      <c r="J79" s="28"/>
+      <c r="K79" s="88"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="88"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="89"/>
+      <c r="I80" s="90"/>
+      <c r="J80" s="28"/>
+      <c r="K80" s="88"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="88"/>
+      <c r="B81" s="28"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="89"/>
+      <c r="I81" s="90"/>
+      <c r="J81" s="28"/>
+      <c r="K81" s="88"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="88"/>
+      <c r="B82" s="28"/>
+      <c r="C82" s="28"/>
+      <c r="D82" s="28"/>
+      <c r="E82" s="28"/>
+      <c r="F82" s="28"/>
+      <c r="G82" s="28"/>
+      <c r="H82" s="89"/>
+      <c r="I82" s="90"/>
+      <c r="J82" s="28"/>
+      <c r="K82" s="88"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="88"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="89"/>
+      <c r="I83" s="90"/>
+      <c r="J83" s="28"/>
+      <c r="K83" s="88"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="88"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
+      <c r="E84" s="28"/>
+      <c r="F84" s="28"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="89"/>
+      <c r="I84" s="90"/>
+      <c r="J84" s="28"/>
+      <c r="K84" s="88"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="88"/>
+      <c r="B85" s="28"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28"/>
+      <c r="H85" s="89"/>
+      <c r="I85" s="90"/>
+      <c r="J85" s="28"/>
+      <c r="K85" s="88"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="88"/>
+      <c r="B86" s="28"/>
+      <c r="C86" s="28"/>
+      <c r="D86" s="28"/>
+      <c r="E86" s="28"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="28"/>
+      <c r="H86" s="89"/>
+      <c r="I86" s="90"/>
+      <c r="J86" s="28"/>
+      <c r="K86" s="88"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="88"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="89"/>
+      <c r="I87" s="90"/>
+      <c r="J87" s="28"/>
+      <c r="K87" s="88"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="88"/>
+      <c r="B88" s="28"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
+      <c r="E88" s="28"/>
+      <c r="F88" s="28"/>
+      <c r="G88" s="28"/>
+      <c r="H88" s="89"/>
+      <c r="I88" s="90"/>
+      <c r="J88" s="28"/>
+      <c r="K88" s="88"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="88"/>
+      <c r="B89" s="28"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
+      <c r="E89" s="28"/>
+      <c r="F89" s="28"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="89"/>
+      <c r="I89" s="90"/>
+      <c r="J89" s="28"/>
+      <c r="K89" s="88"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="88"/>
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="89"/>
+      <c r="I90" s="90"/>
+      <c r="J90" s="28"/>
+      <c r="K90" s="88"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="88"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="89"/>
+      <c r="I91" s="90"/>
+      <c r="J91" s="28"/>
+      <c r="K91" s="88"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="88"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="89"/>
+      <c r="I92" s="90"/>
+      <c r="J92" s="28"/>
+      <c r="K92" s="88"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="88"/>
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="89"/>
+      <c r="I93" s="90"/>
+      <c r="J93" s="28"/>
+      <c r="K93" s="88"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="88"/>
+      <c r="B94" s="28"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28"/>
+      <c r="H94" s="89"/>
+      <c r="I94" s="90"/>
+      <c r="J94" s="28"/>
+      <c r="K94" s="88"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="88"/>
+      <c r="B95" s="28"/>
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="89"/>
+      <c r="I95" s="90"/>
+      <c r="J95" s="28"/>
+      <c r="K95" s="88"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="88"/>
+      <c r="B96" s="28"/>
+      <c r="C96" s="28"/>
+      <c r="D96" s="28"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="28"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="89"/>
+      <c r="I96" s="90"/>
+      <c r="J96" s="28"/>
+      <c r="K96" s="88"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="88"/>
+      <c r="B97" s="28"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="89"/>
+      <c r="I97" s="90"/>
+      <c r="J97" s="28"/>
+      <c r="K97" s="88"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="88"/>
+      <c r="B98" s="28"/>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="89"/>
+      <c r="I98" s="90"/>
+      <c r="J98" s="28"/>
+      <c r="K98" s="88"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="88"/>
+      <c r="B99" s="28"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="28"/>
+      <c r="H99" s="89"/>
+      <c r="I99" s="90"/>
+      <c r="J99" s="28"/>
+      <c r="K99" s="88"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="88"/>
+      <c r="B100" s="28"/>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="F100" s="28"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="89"/>
+      <c r="I100" s="90"/>
+      <c r="J100" s="28"/>
+      <c r="K100" s="88"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="88"/>
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
+      <c r="E101" s="28"/>
+      <c r="F101" s="28"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="89"/>
+      <c r="I101" s="90"/>
+      <c r="J101" s="28"/>
+      <c r="K101" s="88"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="88"/>
+      <c r="B102" s="28"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="28"/>
+      <c r="F102" s="28"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="89"/>
+      <c r="I102" s="90"/>
+      <c r="J102" s="28"/>
+      <c r="K102" s="88"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="88"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="28"/>
+      <c r="H103" s="89"/>
+      <c r="I103" s="90"/>
+      <c r="J103" s="28"/>
+      <c r="K103" s="88"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="88"/>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="28"/>
+      <c r="F104" s="28"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="89"/>
+      <c r="I104" s="90"/>
+      <c r="J104" s="28"/>
+      <c r="K104" s="88"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="88"/>
+      <c r="B105" s="28"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="89"/>
+      <c r="I105" s="90"/>
+      <c r="J105" s="28"/>
+      <c r="K105" s="88"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="88"/>
+      <c r="B106" s="28"/>
+      <c r="C106" s="28"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="28"/>
+      <c r="F106" s="28"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="89"/>
+      <c r="I106" s="90"/>
+      <c r="J106" s="28"/>
+      <c r="K106" s="88"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="88"/>
+      <c r="B107" s="28"/>
+      <c r="C107" s="28"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="28"/>
+      <c r="F107" s="28"/>
+      <c r="G107" s="28"/>
+      <c r="H107" s="89"/>
+      <c r="I107" s="90"/>
+      <c r="J107" s="28"/>
+      <c r="K107" s="88"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="88"/>
+      <c r="B108" s="28"/>
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="F108" s="28"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="89"/>
+      <c r="I108" s="90"/>
+      <c r="J108" s="28"/>
+      <c r="K108" s="88"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="88"/>
+      <c r="B109" s="28"/>
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="89"/>
+      <c r="I109" s="90"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="88"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="88"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="28"/>
+      <c r="D110" s="28"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="28"/>
+      <c r="G110" s="28"/>
+      <c r="H110" s="89"/>
+      <c r="I110" s="90"/>
+      <c r="J110" s="28"/>
+      <c r="K110" s="88"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="88"/>
+      <c r="B111" s="28"/>
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28"/>
+      <c r="H111" s="89"/>
+      <c r="I111" s="90"/>
+      <c r="J111" s="28"/>
+      <c r="K111" s="88"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="88"/>
+      <c r="B112" s="28"/>
+      <c r="C112" s="28"/>
+      <c r="D112" s="28"/>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="89"/>
+      <c r="I112" s="90"/>
+      <c r="J112" s="28"/>
+      <c r="K112" s="88"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="88"/>
+      <c r="B113" s="28"/>
+      <c r="C113" s="28"/>
+      <c r="D113" s="28"/>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="28"/>
+      <c r="H113" s="89"/>
+      <c r="I113" s="90"/>
+      <c r="J113" s="28"/>
+      <c r="K113" s="88"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="88"/>
+      <c r="B114" s="28"/>
+      <c r="C114" s="28"/>
+      <c r="D114" s="28"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+      <c r="G114" s="28"/>
+      <c r="H114" s="89"/>
+      <c r="I114" s="90"/>
+      <c r="J114" s="28"/>
+      <c r="K114" s="88"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="88"/>
+      <c r="B115" s="28"/>
+      <c r="C115" s="28"/>
+      <c r="D115" s="28"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="28"/>
+      <c r="H115" s="89"/>
+      <c r="I115" s="90"/>
+      <c r="J115" s="28"/>
+      <c r="K115" s="88"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="88"/>
+      <c r="B116" s="28"/>
+      <c r="C116" s="28"/>
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="28"/>
+      <c r="G116" s="28"/>
+      <c r="H116" s="89"/>
+      <c r="I116" s="90"/>
+      <c r="J116" s="28"/>
+      <c r="K116" s="88"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="88"/>
+      <c r="B117" s="28"/>
+      <c r="C117" s="28"/>
+      <c r="D117" s="28"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="89"/>
+      <c r="I117" s="90"/>
+      <c r="J117" s="28"/>
+      <c r="K117" s="88"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="88"/>
+      <c r="B118" s="28"/>
+      <c r="C118" s="28"/>
+      <c r="D118" s="28"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28"/>
+      <c r="H118" s="89"/>
+      <c r="I118" s="90"/>
+      <c r="J118" s="28"/>
+      <c r="K118" s="88"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="88"/>
+      <c r="B119" s="28"/>
+      <c r="C119" s="28"/>
+      <c r="D119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="28"/>
+      <c r="H119" s="89"/>
+      <c r="I119" s="90"/>
+      <c r="J119" s="28"/>
+      <c r="K119" s="88"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="88"/>
+      <c r="B120" s="28"/>
+      <c r="C120" s="28"/>
+      <c r="D120" s="28"/>
+      <c r="E120" s="28"/>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="89"/>
+      <c r="I120" s="90"/>
+      <c r="J120" s="28"/>
+      <c r="K120" s="88"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="88"/>
+      <c r="B121" s="28"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="28"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="89"/>
+      <c r="I121" s="90"/>
+      <c r="J121" s="28"/>
+      <c r="K121" s="88"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="88"/>
+      <c r="B122" s="28"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
+      <c r="H122" s="89"/>
+      <c r="I122" s="90"/>
+      <c r="J122" s="28"/>
+      <c r="K122" s="88"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="88"/>
+      <c r="B123" s="28"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="28"/>
+      <c r="E123" s="28"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="28"/>
+      <c r="H123" s="89"/>
+      <c r="I123" s="90"/>
+      <c r="J123" s="28"/>
+      <c r="K123" s="88"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="88"/>
+      <c r="B124" s="28"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="28"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="28"/>
+      <c r="G124" s="28"/>
+      <c r="H124" s="89"/>
+      <c r="I124" s="90"/>
+      <c r="J124" s="28"/>
+      <c r="K124" s="88"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="88"/>
+      <c r="B125" s="28"/>
+      <c r="C125" s="28"/>
+      <c r="D125" s="28"/>
+      <c r="E125" s="28"/>
+      <c r="F125" s="28"/>
+      <c r="G125" s="28"/>
+      <c r="H125" s="89"/>
+      <c r="I125" s="90"/>
+      <c r="J125" s="28"/>
+      <c r="K125" s="88"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="88"/>
+      <c r="B126" s="28"/>
+      <c r="C126" s="28"/>
+      <c r="D126" s="28"/>
+      <c r="E126" s="28"/>
+      <c r="F126" s="28"/>
+      <c r="G126" s="28"/>
+      <c r="H126" s="89"/>
+      <c r="I126" s="90"/>
+      <c r="J126" s="28"/>
+      <c r="K126" s="88"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="88"/>
+      <c r="B127" s="28"/>
+      <c r="C127" s="28"/>
+      <c r="D127" s="28"/>
+      <c r="E127" s="28"/>
+      <c r="F127" s="28"/>
+      <c r="G127" s="28"/>
+      <c r="H127" s="89"/>
+      <c r="I127" s="90"/>
+      <c r="J127" s="28"/>
+      <c r="K127" s="88"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="88"/>
+      <c r="B128" s="28"/>
+      <c r="C128" s="28"/>
+      <c r="D128" s="28"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="89"/>
+      <c r="I128" s="90"/>
+      <c r="J128" s="28"/>
+      <c r="K128" s="88"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="88"/>
+      <c r="B129" s="28"/>
+      <c r="C129" s="28"/>
+      <c r="D129" s="28"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="28"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="89"/>
+      <c r="I129" s="90"/>
+      <c r="J129" s="28"/>
+      <c r="K129" s="88"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="88"/>
+      <c r="B130" s="28"/>
+      <c r="C130" s="28"/>
+      <c r="D130" s="28"/>
+      <c r="E130" s="28"/>
+      <c r="F130" s="28"/>
+      <c r="G130" s="28"/>
+      <c r="H130" s="89"/>
+      <c r="I130" s="90"/>
+      <c r="J130" s="28"/>
+      <c r="K130" s="88"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="88"/>
+      <c r="B131" s="28"/>
+      <c r="C131" s="28"/>
+      <c r="D131" s="28"/>
+      <c r="E131" s="28"/>
+      <c r="F131" s="28"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="89"/>
+      <c r="I131" s="90"/>
+      <c r="J131" s="28"/>
+      <c r="K131" s="88"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="88"/>
+      <c r="B132" s="28"/>
+      <c r="C132" s="28"/>
+      <c r="D132" s="28"/>
+      <c r="E132" s="28"/>
+      <c r="F132" s="28"/>
+      <c r="G132" s="28"/>
+      <c r="H132" s="89"/>
+      <c r="I132" s="90"/>
+      <c r="J132" s="28"/>
+      <c r="K132" s="88"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="88"/>
+      <c r="B133" s="28"/>
+      <c r="C133" s="28"/>
+      <c r="D133" s="28"/>
+      <c r="E133" s="28"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="28"/>
+      <c r="H133" s="89"/>
+      <c r="I133" s="90"/>
+      <c r="J133" s="28"/>
+      <c r="K133" s="88"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="88"/>
+      <c r="B134" s="28"/>
+      <c r="C134" s="28"/>
+      <c r="D134" s="28"/>
+      <c r="E134" s="28"/>
+      <c r="F134" s="28"/>
+      <c r="G134" s="28"/>
+      <c r="H134" s="89"/>
+      <c r="I134" s="90"/>
+      <c r="J134" s="28"/>
+      <c r="K134" s="88"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E15" r:id="rId1" xr:uid="{91F86A27-4DB7-4464-8D72-3977CC7EAA20}"/>
+    <hyperlink ref="E27" r:id="rId2" xr:uid="{1607245A-888D-4792-8F69-FF9BD3217F01}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{9FF5CAAC-174A-4411-AAEE-B32FC992AA1C}">
+            <x14:iconSet iconSet="3Symbols2" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>K2:K150</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>